--- a/results/04_final_refined_daily_hydroclimate_data/601/Avg_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/601/Avg_Temperature_timeseries.xlsx
@@ -708,7 +708,7 @@
         <v>22</v>
       </c>
       <c r="D23">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="24" spans="1:4">
